--- a/data/trans_camb/IP2001-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,16</t>
+          <t>-4,77; 7,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 7,48</t>
+          <t>-5,12; 8,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 2,18</t>
+          <t>-9,17; 1,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 11,38</t>
+          <t>0,75; 11,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 10,68</t>
+          <t>-0,53; 10,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 4,16</t>
+          <t>-5,16; 4,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 7,65</t>
+          <t>-0,86; 7,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 7,36</t>
+          <t>-0,71; 7,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 1,57</t>
+          <t>-5,65; 1,57</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 108,92</t>
+          <t>-42,05; 121,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,9; 116,51</t>
+          <t>-42,63; 133,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,92; 44,34</t>
+          <t>-74,24; 34,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 295,72</t>
+          <t>-2,09; 297,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 287,07</t>
+          <t>-11,7; 258,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,56; 121,87</t>
+          <t>-68,96; 99,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 132,4</t>
+          <t>-11,19; 126,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 128,3</t>
+          <t>-8,86; 128,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,41; 30,7</t>
+          <t>-62,48; 28,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,68</t>
+          <t>-3,4; 6,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 7,12</t>
+          <t>-2,76; 7,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; -0,48</t>
+          <t>-8,91; -0,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 4,32</t>
+          <t>-5,33; 3,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 2,27</t>
+          <t>-6,72; 1,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 3,23</t>
+          <t>-6,09; 3,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 3,74</t>
+          <t>-3,16; 3,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,25</t>
+          <t>-3,36; 3,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 0,41</t>
+          <t>-6,36; 0,17</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 95,63</t>
+          <t>-28,0; 91,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 105,92</t>
+          <t>-25,04; 97,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,1; -4,65</t>
+          <t>-75,05; -5,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 62,7</t>
+          <t>-44,3; 48,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,06; 33,74</t>
+          <t>-56,65; 24,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,22; 47,88</t>
+          <t>-52,09; 43,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 48,07</t>
+          <t>-28,91; 43,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 41,02</t>
+          <t>-31,13; 38,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,34; 5,75</t>
+          <t>-55,52; 3,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 8,28</t>
+          <t>-1,79; 8,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 8,07</t>
+          <t>-2,32; 7,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 1,1</t>
+          <t>-6,98; 1,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 9,35</t>
+          <t>-1,23; 9,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 8,52</t>
+          <t>-2,17; 8,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 1,53</t>
+          <t>-7,4; 1,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 7,27</t>
+          <t>-0,74; 7,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 6,7</t>
+          <t>-0,69; 6,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; -0,11</t>
+          <t>-5,82; 0,02</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 166,59</t>
+          <t>-21,87; 198,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 183,24</t>
+          <t>-27,2; 204,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 31,87</t>
+          <t>-73,05; 38,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 184,05</t>
+          <t>-17,89; 201,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,59; 171,67</t>
+          <t>-22,86; 204,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,76; 39,6</t>
+          <t>-74,25; 31,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 141,15</t>
+          <t>-9,2; 129,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 125,34</t>
+          <t>-9,01; 117,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,4; -0,71</t>
+          <t>-67,92; 3,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 3,1</t>
+          <t>-5,65; 3,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,87</t>
+          <t>-3,31; 6,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,48; -1,3</t>
+          <t>-9,24; -1,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 3,74</t>
+          <t>-5,67; 3,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 7,94</t>
+          <t>-2,13; 8,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,01</t>
+          <t>-7,32; 1,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,88</t>
+          <t>-4,65; 2,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,59</t>
+          <t>-0,96; 6,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,02; -0,86</t>
+          <t>-7,07; -0,74</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,77; 52,04</t>
+          <t>-57,4; 63,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,33; 120,09</t>
+          <t>-32,78; 106,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,59; -11,87</t>
+          <t>-85,87; -14,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,48; 57,3</t>
+          <t>-56,35; 58,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 127,51</t>
+          <t>-21,5; 139,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,63; 33,06</t>
+          <t>-72,63; 30,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 30,61</t>
+          <t>-47,38; 31,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 83,4</t>
+          <t>-10,14; 100,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,7; -8,25</t>
+          <t>-71,76; -7,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,33</t>
+          <t>-1,45; 3,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,59</t>
+          <t>-0,72; 4,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -1,95</t>
+          <t>-6,17; -1,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,8</t>
+          <t>-1,31; 3,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,16</t>
+          <t>-0,65; 4,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,43</t>
+          <t>-4,45; 0,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,0</t>
+          <t>-0,66; 3,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,81</t>
+          <t>0,03; 3,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -1,25</t>
+          <t>-4,53; -1,35</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 45,07</t>
+          <t>-15,29; 50,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 62,88</t>
+          <t>-8,4; 61,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,77; -25,68</t>
+          <t>-64,09; -21,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 54,55</t>
+          <t>-14,33; 55,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 60,9</t>
+          <t>-7,84; 65,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 7,15</t>
+          <t>-46,15; 5,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 40,73</t>
+          <t>-6,94; 40,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,32; 51,64</t>
+          <t>-0,07; 49,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-49,76; -15,91</t>
+          <t>-50,1; -17,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 7,45</t>
+          <t>-4,55; 7,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 8,19</t>
+          <t>-4,27; 8,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 1,73</t>
+          <t>-8,36; 2,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 11,65</t>
+          <t>0,1; 11,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 10,37</t>
+          <t>-0,7; 10,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 4,02</t>
+          <t>-5,24; 3,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 7,54</t>
+          <t>-0,74; 7,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,32</t>
+          <t>-0,64; 7,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,57</t>
+          <t>-5,55; 1,53</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 121,12</t>
+          <t>-39,79; 123,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 133,26</t>
+          <t>-38,64; 128,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,24; 34,03</t>
+          <t>-71,94; 45,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 297,34</t>
+          <t>-1,48; 307,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 258,29</t>
+          <t>-11,64; 287,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,96; 99,87</t>
+          <t>-68,45; 123,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 126,49</t>
+          <t>-9,31; 129,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 128,94</t>
+          <t>-8,66; 130,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,48; 28,59</t>
+          <t>-60,79; 30,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 6,28</t>
+          <t>-3,43; 6,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 7,18</t>
+          <t>-2,74; 7,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; -0,65</t>
+          <t>-8,94; -0,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 3,7</t>
+          <t>-5,26; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 1,85</t>
+          <t>-6,53; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,37</t>
+          <t>-6,4; 2,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 3,54</t>
+          <t>-3,55; 3,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 3,01</t>
+          <t>-3,35; 3,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,17</t>
+          <t>-6,11; 0,43</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 91,46</t>
+          <t>-31,03; 87,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 97,69</t>
+          <t>-24,43; 99,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,05; -5,03</t>
+          <t>-73,65; -0,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,3; 48,89</t>
+          <t>-42,88; 56,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,65; 24,56</t>
+          <t>-54,32; 27,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 43,03</t>
+          <t>-52,46; 42,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 43,62</t>
+          <t>-30,64; 45,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 38,11</t>
+          <t>-29,97; 39,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 3,55</t>
+          <t>-53,71; 8,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 8,66</t>
+          <t>-2,28; 8,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,94</t>
+          <t>-2,56; 7,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 1,64</t>
+          <t>-7,31; 1,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 9,85</t>
+          <t>-1,46; 8,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 8,98</t>
+          <t>-1,81; 8,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 1,51</t>
+          <t>-7,29; 2,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 7,12</t>
+          <t>-0,06; 7,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,53</t>
+          <t>-0,39; 6,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,02</t>
+          <t>-6,04; 0,34</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 198,38</t>
+          <t>-26,19; 197,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 204,47</t>
+          <t>-32,35; 163,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,05; 38,13</t>
+          <t>-76,66; 29,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 201,7</t>
+          <t>-14,13; 185,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 204,48</t>
+          <t>-22,03; 167,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,25; 31,42</t>
+          <t>-74,57; 51,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 129,52</t>
+          <t>-0,8; 139,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 117,67</t>
+          <t>-5,17; 127,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,92; 3,55</t>
+          <t>-67,1; 9,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 3,36</t>
+          <t>-6,01; 3,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 6,34</t>
+          <t>-3,06; 7,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -1,18</t>
+          <t>-9,41; -1,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,57</t>
+          <t>-5,85; 3,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 8,23</t>
+          <t>-2,22; 8,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 1,92</t>
+          <t>-7,13; 1,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,05</t>
+          <t>-4,46; 1,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 6,2</t>
+          <t>-0,89; 6,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,07; -0,74</t>
+          <t>-7,06; -0,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 63,82</t>
+          <t>-56,96; 61,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 106,3</t>
+          <t>-32,56; 121,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-85,87; -14,97</t>
+          <t>-86,3; -15,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 58,9</t>
+          <t>-54,42; 63,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 139,71</t>
+          <t>-23,0; 131,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 30,32</t>
+          <t>-70,45; 41,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 31,34</t>
+          <t>-46,03; 30,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 100,15</t>
+          <t>-10,66; 89,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,76; -7,93</t>
+          <t>-71,71; -6,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,56</t>
+          <t>-1,73; 3,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,6</t>
+          <t>-0,39; 4,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -1,59</t>
+          <t>-6,37; -2,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,78</t>
+          <t>-1,09; 4,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,34</t>
+          <t>-0,72; 4,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,32</t>
+          <t>-4,51; 0,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,03</t>
+          <t>-0,64; 2,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,66</t>
+          <t>-0,04; 3,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -1,35</t>
+          <t>-4,55; -1,36</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 50,27</t>
+          <t>-18,44; 51,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 61,07</t>
+          <t>-5,29; 65,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,09; -21,4</t>
+          <t>-65,93; -27,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 55,0</t>
+          <t>-12,13; 58,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 65,34</t>
+          <t>-8,44; 58,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 5,79</t>
+          <t>-48,1; 5,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 40,94</t>
+          <t>-7,07; 39,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 49,71</t>
+          <t>-0,43; 47,95</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,1; -17,91</t>
+          <t>-50,99; -18,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,57</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,78</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,48</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,57</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-3,37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-2,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 7,76</t>
+          <t>0,2; 11,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 8,21</t>
+          <t>-0,76; 10,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 2,45</t>
+          <t>-4,95; 4,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 11,18</t>
+          <t>-5,03; 7,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 10,16</t>
+          <t>-5,48; 7,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 3,98</t>
+          <t>-8,85; 2,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 7,39</t>
+          <t>-0,35; 7,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 7,48</t>
+          <t>-0,39; 7,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 1,53</t>
+          <t>-5,29; 1,69</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>78,64%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-13,45%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>10,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>16,31%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-38,3%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>95,87%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>78,64%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,75%</t>
+          <t>-37,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-27,83%</t>
+          <t>-27,1%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 123,31</t>
+          <t>-2,69; 295,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 128,67</t>
+          <t>-13,22; 287,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,94; 45,9</t>
+          <t>-64,97; 126,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 307,71</t>
+          <t>-44,37; 108,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 287,93</t>
+          <t>-43,9; 116,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,45; 123,09</t>
+          <t>-73,39; 47,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 129,96</t>
+          <t>-4,76; 132,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 130,72</t>
+          <t>-5,66; 128,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 30,54</t>
+          <t>-60,16; 31,5</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,11</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,54</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-4,61</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-2,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 6,36</t>
+          <t>-5,39; 4,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 7,18</t>
+          <t>-6,29; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -0,07</t>
+          <t>-6,76; 3,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 4,21</t>
+          <t>-3,05; 6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 1,88</t>
+          <t>-2,94; 7,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 2,75</t>
+          <t>-8,93; -0,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,62</t>
+          <t>-3,18; 3,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,16</t>
+          <t>-3,45; 3,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,43</t>
+          <t>-6,32; 0,34</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-6,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-23,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-17,87%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>16,14%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>22,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-47,93%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-6,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-23,91%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,47%</t>
+          <t>-48,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-30,38%</t>
+          <t>-31,24%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 87,57</t>
+          <t>-44,24; 62,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 99,33</t>
+          <t>-53,06; 33,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,65; -0,77</t>
+          <t>-56,49; 42,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 56,48</t>
+          <t>-25,94; 95,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,32; 27,46</t>
+          <t>-24,66; 105,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 42,41</t>
+          <t>-75,18; -5,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 45,64</t>
+          <t>-28,55; 48,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 39,87</t>
+          <t>-31,56; 41,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 8,08</t>
+          <t>-55,73; 5,24</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>3,27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,27</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,92</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,76</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,88</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,27</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,76</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,77</t>
+          <t>-2,03</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 8,32</t>
+          <t>-1,17; 9,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 7,76</t>
+          <t>-1,91; 8,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 1,03</t>
+          <t>-6,72; 2,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 8,98</t>
+          <t>-2,07; 8,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 8,66</t>
+          <t>-1,9; 8,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,02</t>
+          <t>-5,97; 2,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 7,42</t>
+          <t>0,01; 7,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 6,9</t>
+          <t>-0,46; 6,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 0,34</t>
+          <t>-5,63; 0,66</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53,18%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44,82%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-30,59%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>47,58%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>42,56%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-40,12%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>53,18%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44,82%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-37,86%</t>
+          <t>-26,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-39,05%</t>
+          <t>-28,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 197,85</t>
+          <t>-15,1; 184,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 163,21</t>
+          <t>-23,59; 171,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,66; 29,57</t>
+          <t>-68,32; 57,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 185,99</t>
+          <t>-25,13; 166,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 167,67</t>
+          <t>-23,23; 183,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,57; 51,49</t>
+          <t>-67,65; 60,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 139,64</t>
+          <t>0,66; 141,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 127,44</t>
+          <t>-6,21; 125,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,1; 9,56</t>
+          <t>-60,12; 13,71</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,81</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,82</t>
+          <t>-5,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,87</t>
+          <t>-3,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 3,06</t>
+          <t>-5,92; 3,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,04</t>
+          <t>-1,92; 7,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -1,25</t>
+          <t>-7,02; 2,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 3,65</t>
+          <t>-5,98; 3,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 8,03</t>
+          <t>-3,02; 6,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1,96</t>
+          <t>-9,46; -1,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,88</t>
+          <t>-5,04; 1,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 6,31</t>
+          <t>-1,48; 5,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -0,8</t>
+          <t>-6,91; -0,69</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-16,07%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33,52%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-31,01%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-18,87%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>22,42%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-61,96%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-16,07%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-33,82%</t>
+          <t>-61,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-47,13%</t>
+          <t>-46,07%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,96; 61,29</t>
+          <t>-57,48; 57,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 121,05</t>
+          <t>-20,03; 127,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,3; -15,47</t>
+          <t>-69,53; 41,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,42; 63,67</t>
+          <t>-56,77; 52,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 131,25</t>
+          <t>-31,33; 120,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,45; 41,01</t>
+          <t>-86,77; -10,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 30,7</t>
+          <t>-50,93; 30,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 89,75</t>
+          <t>-16,0; 83,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,71; -6,83</t>
+          <t>-69,93; -6,72</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,73</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,06</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,09</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-3,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,68</t>
+          <t>-1,1; 3,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,77</t>
+          <t>-0,7; 4,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -2,0</t>
+          <t>-3,92; 0,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,02</t>
+          <t>-1,54; 3,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,18</t>
+          <t>-0,77; 4,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,36</t>
+          <t>-5,93; -1,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,88</t>
+          <t>-0,66; 3,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,51</t>
+          <t>0,03; 3,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -1,36</t>
+          <t>-4,38; -0,99</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17,89%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-22,58%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>24,4%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-48,49%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-24,84%</t>
+          <t>-45,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,29%</t>
+          <t>-33,78%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 51,43</t>
+          <t>-12,22; 54,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 65,8</t>
+          <t>-8,08; 60,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,93; -27,1</t>
+          <t>-44,79; 9,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 58,14</t>
+          <t>-16,21; 45,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 58,86</t>
+          <t>-7,86; 62,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 5,51</t>
+          <t>-62,86; -22,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 39,14</t>
+          <t>-7,15; 40,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 47,95</t>
+          <t>1,32; 51,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,99; -18,58</t>
+          <t>-47,96; -13,35</t>
         </is>
       </c>
     </row>
